--- a/newsletter/newsletter_base_consolidada.xlsx
+++ b/newsletter/newsletter_base_consolidada.xlsx
@@ -1,21 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoe-my.sharepoint.com/personal/jzurita_ed_ac_uk/Documents/ArboretumMap/newsletter/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_E9AEEF77BF25873C1421F1BAF9147C3AA818AB73" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7AF1031-ADBD-4834-ACFC-38922C4932EF}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Base" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Base" sheetId="1" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" r:id="rId2"/>
+    <sheet name="Nuevos contactos" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Base!$A$1:$H$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$87</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -24,964 +44,1024 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="316">
-  <si>
-    <t xml:space="preserve">email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apellido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">telefono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">institucion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">origen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etiquetas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">consentimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">008marialujan0008@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medina Maria Lujan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223-6878168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">escuela primaria n° 29 Mariano Moreno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta educativa (form) / Form Responses 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">educacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acuibioo@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martínez Soledad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235644108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colegio Naciones Unidas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adrianaveggi@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adriana veggi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235028066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visita botánica (form) / Form Responses 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visita_botanica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">anacor432@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ana Cornejo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2236805796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">andru58buw@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrea Busch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2236324936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">angelinaurbano64@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angelina Urbano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2236854775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aufetpatricia@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patricia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235820049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">auzalorena@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lorena Auza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235753497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">biocca.nicolas@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biocca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contactos y grupos / Familia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contactos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bximartinez@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martinez Bernardo Ignacio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235274744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ees 42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">candela.ledesma@live.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Candela Ledesma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01165655651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">candela_cd@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Candela Camargo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2234541404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carocastanas@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carolina Castanas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235139538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">colonnella.julieta@inta.gob.ar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julieta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colonnella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contactos y grupos / Grupos de Confianza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">combajuanjose@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Jose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">combimdq@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235246390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contactos y grupos / Combis para Translado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cruibal@abc.gob.ar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claudia Ruibal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2236927372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">darthvarda@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Amuchategui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2236835059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ddforestal@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diego</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daeguer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">delfina.maestra@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Delfina Antic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235823250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colegio de las Naciones Unidas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">delgadocamila@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delgado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">542235138819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contactos y grupos / Contactos La Const de Biocca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">doloresjulianatorre@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dolores Juliana Torres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eventos y talleres / Base de Datos Compilada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eventos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ecologia_forestal@yahoo.com.ar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maria Elena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fernandez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emilia.giobio@sustentabledigital.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emilia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estebanlagoph@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lago, Esteban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223-4394391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contactos y grupos / Prov. eventos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fgattesco@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francesco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gattesco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fisicanieves@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nieves Garcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235302724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">floripa024@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Florencia Campo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2233408478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forestalnet@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gmariaflorencia@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maria Florencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gonzalez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">heradri44@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adriana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235045518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taller (form) / Form Responses 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">taller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">info@florbaezfotografia.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flor y Gonzalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223-5036144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jorgasparri@yahoo.com.ar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jorgelina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235346829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">juan.zurita.biocca@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Ignacio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zurita-Biocca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">juaniletamendia@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Ignacio Letamendia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235467829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">julietarodriguezcarlsen@caraludme.edu.ar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julieta Rodriguez Carlsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kgalli@abc.gob.ar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karina galli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02234462129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ep14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ladislaoferrandoa@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ladislao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ferrando</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lauralombardi40@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laura Lombardi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2234216361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E.E.S.T N° 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lauralorenzo130@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laura Lorenzo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2234560718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">liliana.fernandez.2018@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liliana Fernández</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2234559108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lilicolantonio@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liliana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2983457917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lucasgregori2017@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Gregori</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2236702405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nahuel Huapi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">luciladefferrari@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Defferrari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221 6719605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m.dominguez@svpmdp.redfasta.edu.ar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mariana Domínguez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235276164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FASTA San Vicente de Paúl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maleazul@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223 4470536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maria.beck@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Alejandra Beck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02235186260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maritahenales@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maria Cattáneo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2236176373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instituto Gianelli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">martitapereyras@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marta Smart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 4578 2600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">matias.priani@sustentabledigital.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mendezadriana2019@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2236885112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eventos y talleres / 15 Feb 25 VB | Eventos y talleres / Base de Datos Compilada | Visita botánica (form) / Form Responses 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eventos,visita_botanica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mikaela.humanas@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mikku Gonzalez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54 9 2494367897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eventos y talleres / Eventos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monyroitman@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROITMAN MONICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223 154375487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EES N25 LA CHACRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">moreno.fabiana@inta.gob.ar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabiana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moreno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mulazzi.laura@inta.gob.ar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mulazzi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mvictoriavilla@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maria Victoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nicociamarianela2@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marianela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2234983333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nidiagraf@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nidia graf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2236201593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colegio Northern Hills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nieves1507@yahoo.com.ar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nieves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235043105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pablo.ariel.andres@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrés, Pablo Ariel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0223) 581-5421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pamelarivara@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pamela Rivara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235895558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">paulamillenaar@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paula Millenaar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235636851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escuela primaria municipal n 14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pecosbillsmc@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stella Maris Cristeche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235595120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pinceladamarina@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marina Díaz Viel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235187872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secundaria 13 sierras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">privero15@abc.gob.ar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paula Rivero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2234376648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EP 53 JUANA MANSO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">quijadag@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">German Ricardo Quijad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2983647148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rar_89@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ruth Rodriguez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2234550545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escuela Primaria n24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">romicheru98@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romina Cherú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2236842530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rominaressia82@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romina Ressia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2983617281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">s.maraude@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maraude Santiago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223 5920927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">saldivia.mp@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Paula Saldivia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235736460</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sanciveli1977@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sanciveli, María Carola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223-6365450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silvanatrapani@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silvana Trapani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235334293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">solcisk@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARIA SOL KLOSTER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eventos y talleres /  15 Feb 25 METAECO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tabbiamariaagustina@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maria Agustina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabbia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0054 9 (223) 5599542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tamararoxy12@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dell olio Tamara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235216614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tarrafalex@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2233435253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">teclucasmartinez@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Lucas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235280425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tomasoconnor0@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occonor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turismoentandil@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valdez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5492494325459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uranmaria@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ferchu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54 9 2235 21-6044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eventos y talleres / Visitas Escuelas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">urtasunleonel@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leonel urtasun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1128575042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valmdq@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Val- Bus transporte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235217657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">victoriamisto@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Victoria Misto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2234489197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stella Maris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ycorbett179@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yolanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yogaviota69@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabriela Romer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235602216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base de contactos — Newsletter Arboretum La Constancia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consolidada y deduplicada a partir de 5 archivos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contactos únicos (válidos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filas con email halladas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duplicados fusionados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emails inválidos descartados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Por fuente (un contacto puede tener varias)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visita botánica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta educativa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contactos y grupos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eventos y talleres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cómo usar esta base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• La columna 'consentimiento' (amarillo) está vacía a propósito: completala sí/no según corresponda.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Recomendado: antes de sumarlos, enviá un email de bienvenida/re-confirmación (doble opt-in).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• 'origen' indica de qué archivo/hoja salió cada contacto; 'etiquetas' sirve para segmentar en la plataforma.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Para importar a MailerLite/Brevo usá el archivo CSV (newsletter_base_consolidada.csv).</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="337">
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>apellido</t>
+  </si>
+  <si>
+    <t>telefono</t>
+  </si>
+  <si>
+    <t>institucion</t>
+  </si>
+  <si>
+    <t>origen</t>
+  </si>
+  <si>
+    <t>etiquetas</t>
+  </si>
+  <si>
+    <t>consentimiento</t>
+  </si>
+  <si>
+    <t>008marialujan0008@gmail.com</t>
+  </si>
+  <si>
+    <t>Medina Maria Lujan</t>
+  </si>
+  <si>
+    <t>223-6878168</t>
+  </si>
+  <si>
+    <t>escuela primaria n° 29 Mariano Moreno</t>
+  </si>
+  <si>
+    <t>Propuesta educativa (form) / Form Responses 1</t>
+  </si>
+  <si>
+    <t>educacion</t>
+  </si>
+  <si>
+    <t>acuibioo@gmail.com</t>
+  </si>
+  <si>
+    <t>Martínez Soledad</t>
+  </si>
+  <si>
+    <t>2235644108</t>
+  </si>
+  <si>
+    <t>Colegio Naciones Unidas</t>
+  </si>
+  <si>
+    <t>adrianaveggi@hotmail.com</t>
+  </si>
+  <si>
+    <t>Adriana veggi</t>
+  </si>
+  <si>
+    <t>2235028066</t>
+  </si>
+  <si>
+    <t>Visita botánica (form) / Form Responses 1</t>
+  </si>
+  <si>
+    <t>visita_botanica</t>
+  </si>
+  <si>
+    <t>anacor432@gmail.com</t>
+  </si>
+  <si>
+    <t>Ana Cornejo</t>
+  </si>
+  <si>
+    <t>2236805796</t>
+  </si>
+  <si>
+    <t>andru58buw@gmail.com</t>
+  </si>
+  <si>
+    <t>Andrea Busch</t>
+  </si>
+  <si>
+    <t>2236324936</t>
+  </si>
+  <si>
+    <t>angelinaurbano64@gmail.com</t>
+  </si>
+  <si>
+    <t>Angelina Urbano</t>
+  </si>
+  <si>
+    <t>2236854775</t>
+  </si>
+  <si>
+    <t>aufetpatricia@gmail.com</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>2235820049</t>
+  </si>
+  <si>
+    <t>auzalorena@hotmail.com</t>
+  </si>
+  <si>
+    <t>Lorena Auza</t>
+  </si>
+  <si>
+    <t>2235753497</t>
+  </si>
+  <si>
+    <t>biocca.nicolas@gmail.com</t>
+  </si>
+  <si>
+    <t>Nico</t>
+  </si>
+  <si>
+    <t>Biocca</t>
+  </si>
+  <si>
+    <t>Contactos y grupos / Familia</t>
+  </si>
+  <si>
+    <t>contactos</t>
+  </si>
+  <si>
+    <t>bximartinez@gmail.com</t>
+  </si>
+  <si>
+    <t>Martinez Bernardo Ignacio</t>
+  </si>
+  <si>
+    <t>2235274744</t>
+  </si>
+  <si>
+    <t>Ees 42</t>
+  </si>
+  <si>
+    <t>candela.ledesma@live.com</t>
+  </si>
+  <si>
+    <t>Candela Ledesma</t>
+  </si>
+  <si>
+    <t>01165655651</t>
+  </si>
+  <si>
+    <t>candela_cd@hotmail.com</t>
+  </si>
+  <si>
+    <t>María Candela Camargo</t>
+  </si>
+  <si>
+    <t>2234541404</t>
+  </si>
+  <si>
+    <t>carocastanas@gmail.com</t>
+  </si>
+  <si>
+    <t>Carolina Castanas</t>
+  </si>
+  <si>
+    <t>2235139538</t>
+  </si>
+  <si>
+    <t>colonnella.julieta@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>Julieta</t>
+  </si>
+  <si>
+    <t>Colonnella</t>
+  </si>
+  <si>
+    <t>Contactos y grupos / Grupos de Confianza</t>
+  </si>
+  <si>
+    <t>combajuanjose@hotmail.com</t>
+  </si>
+  <si>
+    <t>Juan Jose</t>
+  </si>
+  <si>
+    <t>Comba</t>
+  </si>
+  <si>
+    <t>combimdq@gmail.com</t>
+  </si>
+  <si>
+    <t>Combis</t>
+  </si>
+  <si>
+    <t>2235246390</t>
+  </si>
+  <si>
+    <t>Contactos y grupos / Combis para Translado</t>
+  </si>
+  <si>
+    <t>cruibal@abc.gob.ar</t>
+  </si>
+  <si>
+    <t>Claudia Ruibal</t>
+  </si>
+  <si>
+    <t>2236927372</t>
+  </si>
+  <si>
+    <t>darthvarda@gmail.com</t>
+  </si>
+  <si>
+    <t>María Amuchategui</t>
+  </si>
+  <si>
+    <t>2236835059</t>
+  </si>
+  <si>
+    <t>ddforestal@gmail.com</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
+    <t>Daeguer</t>
+  </si>
+  <si>
+    <t>delfina.maestra@gmail.com</t>
+  </si>
+  <si>
+    <t>María Delfina Antic</t>
+  </si>
+  <si>
+    <t>2235823250</t>
+  </si>
+  <si>
+    <t>Colegio de las Naciones Unidas</t>
+  </si>
+  <si>
+    <t>delgadocamila@hotmail.com</t>
+  </si>
+  <si>
+    <t>Camila</t>
+  </si>
+  <si>
+    <t>Delgado</t>
+  </si>
+  <si>
+    <t>542235138819</t>
+  </si>
+  <si>
+    <t>Contactos y grupos / Contactos La Const de Biocca</t>
+  </si>
+  <si>
+    <t>doloresjulianatorre@gmail.com</t>
+  </si>
+  <si>
+    <t>Dolores Juliana Torres</t>
+  </si>
+  <si>
+    <t>Eventos y talleres / Base de Datos Compilada</t>
+  </si>
+  <si>
+    <t>eventos</t>
+  </si>
+  <si>
+    <t>ecologia_forestal@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>Maria Elena</t>
+  </si>
+  <si>
+    <t>Fernandez</t>
+  </si>
+  <si>
+    <t>emilia.giobio@sustentabledigital.com</t>
+  </si>
+  <si>
+    <t>Emilia</t>
+  </si>
+  <si>
+    <t>estebanlagoph@gmail.com</t>
+  </si>
+  <si>
+    <t>Lago, Esteban</t>
+  </si>
+  <si>
+    <t>223-4394391</t>
+  </si>
+  <si>
+    <t>Contactos y grupos / Prov. eventos</t>
+  </si>
+  <si>
+    <t>fgattesco@hotmail.com</t>
+  </si>
+  <si>
+    <t>Francesco</t>
+  </si>
+  <si>
+    <t>Gattesco</t>
+  </si>
+  <si>
+    <t>fisicanieves@gmail.com</t>
+  </si>
+  <si>
+    <t>Nieves Garcia</t>
+  </si>
+  <si>
+    <t>2235302724</t>
+  </si>
+  <si>
+    <t>floripa024@gmail.com</t>
+  </si>
+  <si>
+    <t>María Florencia Campo</t>
+  </si>
+  <si>
+    <t>2233408478</t>
+  </si>
+  <si>
+    <t>forestalnet@gmail.com</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>gmariaflorencia@gmail.com</t>
+  </si>
+  <si>
+    <t>Maria Florencia</t>
+  </si>
+  <si>
+    <t>Gonzalez</t>
+  </si>
+  <si>
+    <t>heradri44@hotmail.com</t>
+  </si>
+  <si>
+    <t>Adriana</t>
+  </si>
+  <si>
+    <t>2235045518</t>
+  </si>
+  <si>
+    <t>Taller (form) / Form Responses 1</t>
+  </si>
+  <si>
+    <t>taller</t>
+  </si>
+  <si>
+    <t>info@florbaezfotografia.com</t>
+  </si>
+  <si>
+    <t>Flor y Gonzalo</t>
+  </si>
+  <si>
+    <t>223-5036144</t>
+  </si>
+  <si>
+    <t>jorgasparri@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>Jorgelina</t>
+  </si>
+  <si>
+    <t>2235346829</t>
+  </si>
+  <si>
+    <t>juan.zurita.biocca@gmail.com</t>
+  </si>
+  <si>
+    <t>Juan Ignacio</t>
+  </si>
+  <si>
+    <t>Zurita-Biocca</t>
+  </si>
+  <si>
+    <t>juaniletamendia@gmail.com</t>
+  </si>
+  <si>
+    <t>Juan Ignacio Letamendia</t>
+  </si>
+  <si>
+    <t>2235467829</t>
+  </si>
+  <si>
+    <t>julietarodriguezcarlsen@caraludme.edu.ar</t>
+  </si>
+  <si>
+    <t>Julieta Rodriguez Carlsen</t>
+  </si>
+  <si>
+    <t>kgalli@abc.gob.ar</t>
+  </si>
+  <si>
+    <t>Karina galli</t>
+  </si>
+  <si>
+    <t>02234462129</t>
+  </si>
+  <si>
+    <t>Ep14</t>
+  </si>
+  <si>
+    <t>ladislaoferrandoa@gmail.com</t>
+  </si>
+  <si>
+    <t>Ladislao</t>
+  </si>
+  <si>
+    <t>Ferrando</t>
+  </si>
+  <si>
+    <t>lauralombardi40@gmail.com</t>
+  </si>
+  <si>
+    <t>Laura Lombardi</t>
+  </si>
+  <si>
+    <t>2234216361</t>
+  </si>
+  <si>
+    <t>E.E.S.T N° 1</t>
+  </si>
+  <si>
+    <t>lauralorenzo130@gmail.com</t>
+  </si>
+  <si>
+    <t>Laura Lorenzo</t>
+  </si>
+  <si>
+    <t>2234560718</t>
+  </si>
+  <si>
+    <t>liliana.fernandez.2018@hotmail.com</t>
+  </si>
+  <si>
+    <t>Liliana Fernández</t>
+  </si>
+  <si>
+    <t>2234559108</t>
+  </si>
+  <si>
+    <t>lilicolantonio@hotmail.com</t>
+  </si>
+  <si>
+    <t>Liliana</t>
+  </si>
+  <si>
+    <t>2983457917</t>
+  </si>
+  <si>
+    <t>lucasgregori2017@gmail.com</t>
+  </si>
+  <si>
+    <t>Lucas Gregori</t>
+  </si>
+  <si>
+    <t>2236702405</t>
+  </si>
+  <si>
+    <t>Nahuel Huapi</t>
+  </si>
+  <si>
+    <t>luciladefferrari@gmail.com</t>
+  </si>
+  <si>
+    <t>Lucila</t>
+  </si>
+  <si>
+    <t>Defferrari</t>
+  </si>
+  <si>
+    <t>221 6719605</t>
+  </si>
+  <si>
+    <t>m.dominguez@svpmdp.redfasta.edu.ar</t>
+  </si>
+  <si>
+    <t>Mariana Domínguez</t>
+  </si>
+  <si>
+    <t>2235276164</t>
+  </si>
+  <si>
+    <t>FASTA San Vicente de Paúl</t>
+  </si>
+  <si>
+    <t>maleazul@gmail.com</t>
+  </si>
+  <si>
+    <t>María</t>
+  </si>
+  <si>
+    <t>223 4470536</t>
+  </si>
+  <si>
+    <t>maria.beck@hotmail.com</t>
+  </si>
+  <si>
+    <t>María Alejandra Beck</t>
+  </si>
+  <si>
+    <t>02235186260</t>
+  </si>
+  <si>
+    <t>maritahenales@gmail.com</t>
+  </si>
+  <si>
+    <t>Maria Cattáneo</t>
+  </si>
+  <si>
+    <t>2236176373</t>
+  </si>
+  <si>
+    <t>Instituto Gianelli</t>
+  </si>
+  <si>
+    <t>martitapereyras@gmail.com</t>
+  </si>
+  <si>
+    <t>Marta Smart</t>
+  </si>
+  <si>
+    <t>11 4578 2600</t>
+  </si>
+  <si>
+    <t>matias.priani@sustentabledigital.com</t>
+  </si>
+  <si>
+    <t>Matias</t>
+  </si>
+  <si>
+    <t>mendezadriana2019@gmail.com</t>
+  </si>
+  <si>
+    <t>2236885112</t>
+  </si>
+  <si>
+    <t>Eventos y talleres / 15 Feb 25 VB | Eventos y talleres / Base de Datos Compilada | Visita botánica (form) / Form Responses 1</t>
+  </si>
+  <si>
+    <t>eventos,visita_botanica</t>
+  </si>
+  <si>
+    <t>mikaela.humanas@gmail.com</t>
+  </si>
+  <si>
+    <t>Mikku Gonzalez</t>
+  </si>
+  <si>
+    <t>54 9 2494367897</t>
+  </si>
+  <si>
+    <t>Eventos y talleres / Eventos</t>
+  </si>
+  <si>
+    <t>monyroitman@gmail.com</t>
+  </si>
+  <si>
+    <t>ROITMAN MONICA</t>
+  </si>
+  <si>
+    <t>223 154375487</t>
+  </si>
+  <si>
+    <t>EES N25 LA CHACRA</t>
+  </si>
+  <si>
+    <t>moreno.fabiana@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>Fabiana</t>
+  </si>
+  <si>
+    <t>Moreno</t>
+  </si>
+  <si>
+    <t>mulazzi.laura@inta.gob.ar</t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>Mulazzi</t>
+  </si>
+  <si>
+    <t>mvictoriavilla@hotmail.com</t>
+  </si>
+  <si>
+    <t>Maria Victoria</t>
+  </si>
+  <si>
+    <t>Villa</t>
+  </si>
+  <si>
+    <t>nicociamarianela2@hotmail.com</t>
+  </si>
+  <si>
+    <t>Marianela</t>
+  </si>
+  <si>
+    <t>2234983333</t>
+  </si>
+  <si>
+    <t>nidiagraf@gmail.com</t>
+  </si>
+  <si>
+    <t>nidia graf</t>
+  </si>
+  <si>
+    <t>2236201593</t>
+  </si>
+  <si>
+    <t>Colegio Northern Hills</t>
+  </si>
+  <si>
+    <t>nieves1507@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>Nieves</t>
+  </si>
+  <si>
+    <t>2235043105</t>
+  </si>
+  <si>
+    <t>pablo.ariel.andres@gmail.com</t>
+  </si>
+  <si>
+    <t>Andrés, Pablo Ariel</t>
+  </si>
+  <si>
+    <t>(0223) 581-5421</t>
+  </si>
+  <si>
+    <t>pamelarivara@gmail.com</t>
+  </si>
+  <si>
+    <t>Pamela Rivara</t>
+  </si>
+  <si>
+    <t>2235895558</t>
+  </si>
+  <si>
+    <t>paulamillenaar@gmail.com</t>
+  </si>
+  <si>
+    <t>Paula Millenaar</t>
+  </si>
+  <si>
+    <t>2235636851</t>
+  </si>
+  <si>
+    <t>Escuela primaria municipal n 14</t>
+  </si>
+  <si>
+    <t>pecosbillsmc@hotmail.com</t>
+  </si>
+  <si>
+    <t>Stella Maris Cristeche</t>
+  </si>
+  <si>
+    <t>2235595120</t>
+  </si>
+  <si>
+    <t>IAMA</t>
+  </si>
+  <si>
+    <t>pinceladamarina@gmail.com</t>
+  </si>
+  <si>
+    <t>Marina Díaz Viel</t>
+  </si>
+  <si>
+    <t>2235187872</t>
+  </si>
+  <si>
+    <t>Secundaria 13 sierras</t>
+  </si>
+  <si>
+    <t>privero15@abc.gob.ar</t>
+  </si>
+  <si>
+    <t>Paula Rivero</t>
+  </si>
+  <si>
+    <t>2234376648</t>
+  </si>
+  <si>
+    <t>EP 53 JUANA MANSO</t>
+  </si>
+  <si>
+    <t>quijadag@hotmail.com</t>
+  </si>
+  <si>
+    <t>German Ricardo Quijad</t>
+  </si>
+  <si>
+    <t>2983647148</t>
+  </si>
+  <si>
+    <t>rar_89@hotmail.com</t>
+  </si>
+  <si>
+    <t>Ruth Rodriguez</t>
+  </si>
+  <si>
+    <t>2234550545</t>
+  </si>
+  <si>
+    <t>Escuela Primaria n24</t>
+  </si>
+  <si>
+    <t>romicheru98@gmail.com</t>
+  </si>
+  <si>
+    <t>Romina Cherú</t>
+  </si>
+  <si>
+    <t>2236842530</t>
+  </si>
+  <si>
+    <t>rominaressia82@gmail.com</t>
+  </si>
+  <si>
+    <t>Romina Ressia</t>
+  </si>
+  <si>
+    <t>2983617281</t>
+  </si>
+  <si>
+    <t>s.maraude@gmail.com</t>
+  </si>
+  <si>
+    <t>Maraude Santiago</t>
+  </si>
+  <si>
+    <t>223 5920927</t>
+  </si>
+  <si>
+    <t>saldivia.mp@gmail.com</t>
+  </si>
+  <si>
+    <t>María Paula Saldivia</t>
+  </si>
+  <si>
+    <t>2235736460</t>
+  </si>
+  <si>
+    <t>sanciveli1977@gmail.com</t>
+  </si>
+  <si>
+    <t>Sanciveli, María Carola</t>
+  </si>
+  <si>
+    <t>223-6365450</t>
+  </si>
+  <si>
+    <t>silvanatrapani@gmail.com</t>
+  </si>
+  <si>
+    <t>Silvana Trapani</t>
+  </si>
+  <si>
+    <t>2235334293</t>
+  </si>
+  <si>
+    <t>solcisk@gmail.com</t>
+  </si>
+  <si>
+    <t>MARIA SOL KLOSTER</t>
+  </si>
+  <si>
+    <t>Eventos y talleres /  15 Feb 25 METAECO</t>
+  </si>
+  <si>
+    <t>tabbiamariaagustina@gmail.com</t>
+  </si>
+  <si>
+    <t>Maria Agustina</t>
+  </si>
+  <si>
+    <t>Tabbia</t>
+  </si>
+  <si>
+    <t>0054 9 (223) 5599542</t>
+  </si>
+  <si>
+    <t>tamararoxy12@gmail.com</t>
+  </si>
+  <si>
+    <t>Dell olio Tamara</t>
+  </si>
+  <si>
+    <t>2235216614</t>
+  </si>
+  <si>
+    <t>tarrafalex@gmail.com</t>
+  </si>
+  <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>2233435253</t>
+  </si>
+  <si>
+    <t>teclucasmartinez@gmail.com</t>
+  </si>
+  <si>
+    <t>Juan Lucas</t>
+  </si>
+  <si>
+    <t>2235280425</t>
+  </si>
+  <si>
+    <t>tomasoconnor0@gmail.com</t>
+  </si>
+  <si>
+    <t>Tomas</t>
+  </si>
+  <si>
+    <t>Occonor</t>
+  </si>
+  <si>
+    <t>turismoentandil@gmail.com</t>
+  </si>
+  <si>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t>Valdez</t>
+  </si>
+  <si>
+    <t>5492494325459</t>
+  </si>
+  <si>
+    <t>uranmaria@gmail.com</t>
+  </si>
+  <si>
+    <t>Ferchu</t>
+  </si>
+  <si>
+    <t>54 9 2235 21-6044</t>
+  </si>
+  <si>
+    <t>Eventos y talleres / Visitas Escuelas</t>
+  </si>
+  <si>
+    <t>urtasunleonel@gmail.com</t>
+  </si>
+  <si>
+    <t>Leonel urtasun</t>
+  </si>
+  <si>
+    <t>1128575042</t>
+  </si>
+  <si>
+    <t>valmdq@hotmail.com</t>
+  </si>
+  <si>
+    <t>Val- Bus transporte</t>
+  </si>
+  <si>
+    <t>2235217657</t>
+  </si>
+  <si>
+    <t>victoriamisto@hotmail.com</t>
+  </si>
+  <si>
+    <t>María Victoria Misto</t>
+  </si>
+  <si>
+    <t>2234489197</t>
+  </si>
+  <si>
+    <t>Stella Maris</t>
+  </si>
+  <si>
+    <t>ycorbett179@gmail.com</t>
+  </si>
+  <si>
+    <t>Yolanda</t>
+  </si>
+  <si>
+    <t>yogaviota69@gmail.com</t>
+  </si>
+  <si>
+    <t>Gabriela Romer</t>
+  </si>
+  <si>
+    <t>2235602216</t>
+  </si>
+  <si>
+    <t>Base de contactos — Newsletter Arboretum La Constancia</t>
+  </si>
+  <si>
+    <t>Consolidada y deduplicada a partir de 5 archivos.</t>
+  </si>
+  <si>
+    <t>Contactos únicos (válidos)</t>
+  </si>
+  <si>
+    <t>Filas con email halladas</t>
+  </si>
+  <si>
+    <t>Duplicados fusionados</t>
+  </si>
+  <si>
+    <t>Emails inválidos descartados</t>
+  </si>
+  <si>
+    <t>Por fuente (un contacto puede tener varias)</t>
+  </si>
+  <si>
+    <t>Visita botánica</t>
+  </si>
+  <si>
+    <t>Propuesta educativa</t>
+  </si>
+  <si>
+    <t>Contactos y grupos</t>
+  </si>
+  <si>
+    <t>Taller</t>
+  </si>
+  <si>
+    <t>Eventos y talleres</t>
+  </si>
+  <si>
+    <t>Cómo usar esta base</t>
+  </si>
+  <si>
+    <t>• La columna 'consentimiento' (amarillo) está vacía a propósito: completala sí/no según corresponda.</t>
+  </si>
+  <si>
+    <t>• Recomendado: antes de sumarlos, enviá un email de bienvenida/re-confirmación (doble opt-in).</t>
+  </si>
+  <si>
+    <t>• 'origen' indica de qué archivo/hoja salió cada contacto; 'etiquetas' sirve para segmentar en la plataforma.</t>
+  </si>
+  <si>
+    <t>• Para importar a MailerLite/Brevo usá el archivo CSV (newsletter_base_consolidada.csv).</t>
+  </si>
+  <si>
+    <t>anacarinadosso@gmail.com</t>
+  </si>
+  <si>
+    <t>Ana Carina</t>
+  </si>
+  <si>
+    <t>Dosso</t>
+  </si>
+  <si>
+    <t>mjf1802@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>rociopellejero@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>Pueblasmariadelosangeles59@gmail.com</t>
+  </si>
+  <si>
+    <t>Naomicaceres2204@gmail.com</t>
+  </si>
+  <si>
+    <t>goldenpetrucci@gmail.com</t>
+  </si>
+  <si>
+    <t>caritomenna@gmail.com</t>
+  </si>
+  <si>
+    <t>Maria de los Angeles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María José </t>
+  </si>
+  <si>
+    <t>Francia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rocio Nair </t>
+  </si>
+  <si>
+    <t>Pellejero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naomi </t>
+  </si>
+  <si>
+    <t>Caceres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden </t>
+  </si>
+  <si>
+    <t>Petrucci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carolina </t>
+  </si>
+  <si>
+    <t>Menna</t>
+  </si>
+  <si>
+    <t>Paseo Fotografico</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -990,62 +1070,55 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="13"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF444444"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1069,7 +1142,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -1077,106 +1150,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1E4A38"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF3B0"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1235,51 +1232,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF444444"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1287,12 +1296,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1321,7 +1330,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1342,7 +1351,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1393,7 +1402,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1411,32 +1420,31 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H87"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="42" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1462,7 +1470,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1484,7 +1492,7 @@
       </c>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -1506,7 +1514,7 @@
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
@@ -1526,7 +1534,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1546,7 +1554,7 @@
       </c>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -1566,7 +1574,7 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
@@ -1586,7 +1594,7 @@
       </c>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -1606,7 +1614,7 @@
       </c>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>35</v>
       </c>
@@ -1626,7 +1634,7 @@
       </c>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
@@ -1646,7 +1654,7 @@
       </c>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>43</v>
       </c>
@@ -1668,7 +1676,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>47</v>
       </c>
@@ -1688,7 +1696,7 @@
       </c>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>50</v>
       </c>
@@ -1708,7 +1716,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>53</v>
       </c>
@@ -1728,7 +1736,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>56</v>
       </c>
@@ -1748,7 +1756,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>60</v>
       </c>
@@ -1768,7 +1776,7 @@
       </c>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>63</v>
       </c>
@@ -1788,7 +1796,7 @@
       </c>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>67</v>
       </c>
@@ -1808,7 +1816,7 @@
       </c>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>70</v>
       </c>
@@ -1828,7 +1836,7 @@
       </c>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>73</v>
       </c>
@@ -1848,7 +1856,7 @@
       </c>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>76</v>
       </c>
@@ -1870,7 +1878,7 @@
       </c>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>80</v>
       </c>
@@ -1892,7 +1900,7 @@
       </c>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>85</v>
       </c>
@@ -1912,7 +1920,7 @@
       </c>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>89</v>
       </c>
@@ -1932,7 +1940,7 @@
       </c>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>92</v>
       </c>
@@ -1950,7 +1958,7 @@
       </c>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>94</v>
       </c>
@@ -1970,7 +1978,7 @@
       </c>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>98</v>
       </c>
@@ -1990,7 +1998,7 @@
       </c>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>101</v>
       </c>
@@ -2010,7 +2018,7 @@
       </c>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>104</v>
       </c>
@@ -2030,7 +2038,7 @@
       </c>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>107</v>
       </c>
@@ -2050,7 +2058,7 @@
       </c>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>110</v>
       </c>
@@ -2070,7 +2078,7 @@
       </c>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>113</v>
       </c>
@@ -2090,7 +2098,7 @@
       </c>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>118</v>
       </c>
@@ -2110,7 +2118,7 @@
       </c>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>121</v>
       </c>
@@ -2130,7 +2138,7 @@
       </c>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>124</v>
       </c>
@@ -2150,7 +2158,7 @@
       </c>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>127</v>
       </c>
@@ -2170,7 +2178,7 @@
       </c>
       <c r="H36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>130</v>
       </c>
@@ -2190,7 +2198,7 @@
       </c>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>132</v>
       </c>
@@ -2212,7 +2220,7 @@
       </c>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>136</v>
       </c>
@@ -2232,7 +2240,7 @@
       </c>
       <c r="H39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>139</v>
       </c>
@@ -2254,7 +2262,7 @@
       </c>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>143</v>
       </c>
@@ -2274,7 +2282,7 @@
       </c>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>146</v>
       </c>
@@ -2294,7 +2302,7 @@
       </c>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>149</v>
       </c>
@@ -2314,7 +2322,7 @@
       </c>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>152</v>
       </c>
@@ -2336,7 +2344,7 @@
       </c>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>156</v>
       </c>
@@ -2358,7 +2366,7 @@
       </c>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>160</v>
       </c>
@@ -2380,7 +2388,7 @@
       </c>
       <c r="H46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>164</v>
       </c>
@@ -2400,7 +2408,7 @@
       </c>
       <c r="H47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>167</v>
       </c>
@@ -2420,7 +2428,7 @@
       </c>
       <c r="H48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>170</v>
       </c>
@@ -2442,7 +2450,7 @@
       </c>
       <c r="H49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>174</v>
       </c>
@@ -2462,7 +2470,7 @@
       </c>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>177</v>
       </c>
@@ -2480,7 +2488,7 @@
       </c>
       <c r="H51" s="3"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>179</v>
       </c>
@@ -2500,7 +2508,7 @@
       </c>
       <c r="H52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>183</v>
       </c>
@@ -2520,7 +2528,7 @@
       </c>
       <c r="H53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>187</v>
       </c>
@@ -2542,7 +2550,7 @@
       </c>
       <c r="H54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>191</v>
       </c>
@@ -2562,7 +2570,7 @@
       </c>
       <c r="H55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>194</v>
       </c>
@@ -2582,7 +2590,7 @@
       </c>
       <c r="H56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>197</v>
       </c>
@@ -2602,7 +2610,7 @@
       </c>
       <c r="H57" s="3"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>200</v>
       </c>
@@ -2622,7 +2630,7 @@
       </c>
       <c r="H58" s="3"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>203</v>
       </c>
@@ -2644,7 +2652,7 @@
       </c>
       <c r="H59" s="3"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>207</v>
       </c>
@@ -2664,7 +2672,7 @@
       </c>
       <c r="H60" s="3"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>210</v>
       </c>
@@ -2684,7 +2692,7 @@
       </c>
       <c r="H61" s="3"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>213</v>
       </c>
@@ -2704,7 +2712,7 @@
       </c>
       <c r="H62" s="3"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>216</v>
       </c>
@@ -2726,7 +2734,7 @@
       </c>
       <c r="H63" s="3"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>220</v>
       </c>
@@ -2748,7 +2756,7 @@
       </c>
       <c r="H64" s="3"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>224</v>
       </c>
@@ -2770,7 +2778,7 @@
       </c>
       <c r="H65" s="3"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>228</v>
       </c>
@@ -2792,7 +2800,7 @@
       </c>
       <c r="H66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>232</v>
       </c>
@@ -2812,7 +2820,7 @@
       </c>
       <c r="H67" s="3"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>235</v>
       </c>
@@ -2834,7 +2842,7 @@
       </c>
       <c r="H68" s="3"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>239</v>
       </c>
@@ -2854,7 +2862,7 @@
       </c>
       <c r="H69" s="3"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>242</v>
       </c>
@@ -2876,7 +2884,7 @@
       </c>
       <c r="H70" s="3"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>245</v>
       </c>
@@ -2896,7 +2904,7 @@
       </c>
       <c r="H71" s="3"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>248</v>
       </c>
@@ -2916,7 +2924,7 @@
       </c>
       <c r="H72" s="3"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>251</v>
       </c>
@@ -2938,7 +2946,7 @@
       </c>
       <c r="H73" s="3"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>254</v>
       </c>
@@ -2958,7 +2966,7 @@
       </c>
       <c r="H74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>257</v>
       </c>
@@ -2976,7 +2984,7 @@
       </c>
       <c r="H75" s="3"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>260</v>
       </c>
@@ -2998,7 +3006,7 @@
       </c>
       <c r="H76" s="3"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>264</v>
       </c>
@@ -3020,7 +3028,7 @@
       </c>
       <c r="H77" s="3"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>267</v>
       </c>
@@ -3040,7 +3048,7 @@
       </c>
       <c r="H78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>270</v>
       </c>
@@ -3060,7 +3068,7 @@
       </c>
       <c r="H79" s="3"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>273</v>
       </c>
@@ -3080,7 +3088,7 @@
       </c>
       <c r="H80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>276</v>
       </c>
@@ -3102,7 +3110,7 @@
       </c>
       <c r="H81" s="3"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>280</v>
       </c>
@@ -3122,7 +3130,7 @@
       </c>
       <c r="H82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>284</v>
       </c>
@@ -3142,7 +3150,7 @@
       </c>
       <c r="H83" s="3"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>287</v>
       </c>
@@ -3162,7 +3170,7 @@
       </c>
       <c r="H84" s="3"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>290</v>
       </c>
@@ -3184,7 +3192,7 @@
       </c>
       <c r="H85" s="3"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>294</v>
       </c>
@@ -3204,7 +3212,7 @@
       </c>
       <c r="H86" s="3"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>296</v>
       </c>
@@ -3225,155 +3233,302 @@
       <c r="H87" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H87"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:H87" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col min="1" max="1" width="64" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <f aca="false">COUNTA(Base!A2:A87)</f>
+      <c r="B4" s="2">
+        <f>COUNTA(Base!A2:A87)</f>
         <v>86</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="2">
         <v>93</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B10" s="2" t="n">
-        <f aca="false">COUNTIF(Base!$G$2:$G$87,"*visita_botanica*")</f>
+      <c r="B10" s="2">
+        <f>COUNTIF(Base!$G$2:$G$87,"*visita_botanica*")</f>
         <v>29</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B11" s="2" t="n">
-        <f aca="false">COUNTIF(Base!$G$2:$G$87,"*educacion*")</f>
+      <c r="B11" s="2">
+        <f>COUNTIF(Base!$G$2:$G$87,"*educacion*")</f>
         <v>20</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B12" s="2" t="n">
-        <f aca="false">COUNTIF(Base!$G$2:$G$87,"*contactos*")</f>
+      <c r="B12" s="2">
+        <f>COUNTIF(Base!$G$2:$G$87,"*contactos*")</f>
         <v>27</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B13" s="2" t="n">
-        <f aca="false">COUNTIF(Base!$G$2:$G$87,"*taller*")</f>
+      <c r="B13" s="2">
+        <f>COUNTIF(Base!$G$2:$G$87,"*taller*")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B14" s="2" t="n">
-        <f aca="false">COUNTIF(Base!$G$2:$G$87,"*eventos*")</f>
+      <c r="B14" s="2">
+        <f>COUNTIF(Base!$G$2:$G$87,"*eventos*")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>315</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB5A2A20-4014-4FFF-9A5A-0B4B4EA9E549}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="35.7265625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="B2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D2" s="9">
+        <v>2235951482</v>
+      </c>
+      <c r="F2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="B3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D3" s="9">
+        <v>2235485135</v>
+      </c>
+      <c r="F3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="B4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2235418503</v>
+      </c>
+      <c r="F4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B5" t="s">
+        <v>325</v>
+      </c>
+      <c r="D5" s="9">
+        <v>2235747922</v>
+      </c>
+      <c r="F5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D6" s="9">
+        <v>2236980263</v>
+      </c>
+      <c r="F6" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="B7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" t="s">
+        <v>333</v>
+      </c>
+      <c r="D7" s="9">
+        <v>2235444704</v>
+      </c>
+      <c r="F7" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="B8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" t="s">
+        <v>335</v>
+      </c>
+      <c r="D8" s="9">
+        <v>2236337845</v>
+      </c>
+      <c r="F8" t="s">
+        <v>336</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{D6475189-F4C5-4113-9083-FA0E6946B9E6}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/newsletter/newsletter_base_consolidada.xlsx
+++ b/newsletter/newsletter_base_consolidada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoe-my.sharepoint.com/personal/jzurita_ed_ac_uk/Documents/ArboretumMap/newsletter/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_E9AEEF77BF25873C1421F1BAF9147C3AA818AB73" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7AF1031-ADBD-4834-ACFC-38922C4932EF}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_E9AEEF77BF25873C1421F1BAF9147C3AA818AB73" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D53D5E0-2256-48B6-A94F-C9ED2A7E69B0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="336">
   <si>
     <t>email</t>
   </si>
@@ -1040,9 +1040,6 @@
   </si>
   <si>
     <t>Caceres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golden </t>
   </si>
   <si>
     <t>Petrucci</t>
@@ -3380,7 +3377,9 @@
     <col min="1" max="1" width="35.7265625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" customWidth="1"/>
     <col min="5" max="5" width="10.7265625" customWidth="1"/>
+    <col min="7" max="7" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -3423,7 +3422,7 @@
         <v>2235951482</v>
       </c>
       <c r="F2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -3440,7 +3439,7 @@
         <v>2235485135</v>
       </c>
       <c r="F3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -3457,7 +3456,7 @@
         <v>2235418503</v>
       </c>
       <c r="F4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -3471,7 +3470,7 @@
         <v>2235747922</v>
       </c>
       <c r="F5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -3488,7 +3487,7 @@
         <v>2236980263</v>
       </c>
       <c r="F6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -3496,16 +3495,16 @@
         <v>323</v>
       </c>
       <c r="B7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" t="s">
         <v>332</v>
-      </c>
-      <c r="C7" t="s">
-        <v>333</v>
       </c>
       <c r="D7" s="9">
         <v>2235444704</v>
       </c>
       <c r="F7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -3513,16 +3512,16 @@
         <v>324</v>
       </c>
       <c r="B8" t="s">
+        <v>333</v>
+      </c>
+      <c r="C8" t="s">
         <v>334</v>
-      </c>
-      <c r="C8" t="s">
-        <v>335</v>
       </c>
       <c r="D8" s="9">
         <v>2236337845</v>
       </c>
       <c r="F8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
